--- a/artfynd/A 60500-2025 artfynd.xlsx
+++ b/artfynd/A 60500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688517</v>
       </c>
       <c r="B2" t="n">
-        <v>80224</v>
+        <v>80227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60500-2025 artfynd.xlsx
+++ b/artfynd/A 60500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688517</v>
       </c>
       <c r="B2" t="n">
-        <v>80227</v>
+        <v>80228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60500-2025 artfynd.xlsx
+++ b/artfynd/A 60500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688517</v>
       </c>
       <c r="B2" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60500-2025 artfynd.xlsx
+++ b/artfynd/A 60500-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,112 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130210344</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80235</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Laxede, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>767432</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7361194</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60500-2025 artfynd.xlsx
+++ b/artfynd/A 60500-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>130210344</v>
       </c>
       <c r="B3" t="n">
-        <v>80235</v>
+        <v>80320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60500-2025 artfynd.xlsx
+++ b/artfynd/A 60500-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>130210344</v>
       </c>
       <c r="B3" t="n">
-        <v>80320</v>
+        <v>80323</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60500-2025 artfynd.xlsx
+++ b/artfynd/A 60500-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>130210344</v>
       </c>
       <c r="B3" t="n">
-        <v>80323</v>
+        <v>80349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60500-2025 artfynd.xlsx
+++ b/artfynd/A 60500-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>130210344</v>
       </c>
       <c r="B3" t="n">
-        <v>80349</v>
+        <v>80351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
